--- a/data/trans_orig/P20-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P20-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses en 2007</t>
+          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17348</t>
+          <t>17637</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6778</t>
+          <t>6875</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21895</t>
+          <t>21672</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14986</t>
+          <t>14306</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34020</t>
+          <t>34068</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>255662</t>
+          <t>255373</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>267639</t>
+          <t>267608</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>238943</t>
+          <t>239166</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>254060</t>
+          <t>253963</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>499828</t>
+          <t>499780</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>518862</t>
+          <t>519542</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,32%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16028</t>
+          <t>17659</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36929</t>
+          <t>38106</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36109</t>
+          <t>34725</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62523</t>
+          <t>60453</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57144</t>
+          <t>58154</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>89853</t>
+          <t>90188</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>456146</t>
+          <t>454969</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>477047</t>
+          <t>475416</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>441426</t>
+          <t>443496</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>467840</t>
+          <t>469224</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>907171</t>
+          <t>906836</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>939880</t>
+          <t>938870</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,17%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15765</t>
+          <t>16774</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10256</t>
+          <t>9362</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25748</t>
+          <t>24675</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14573</t>
+          <t>15851</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33485</t>
+          <t>36714</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>303081</t>
+          <t>302072</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>316228</t>
+          <t>315302</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>309664</t>
+          <t>310737</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>325156</t>
+          <t>326050</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>620773</t>
+          <t>617544</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>639685</t>
+          <t>638407</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3485</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13698</t>
+          <t>14584</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12612</t>
+          <t>11998</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30113</t>
+          <t>29777</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18871</t>
+          <t>17907</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39100</t>
+          <t>37498</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>344029</t>
+          <t>343143</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>354242</t>
+          <t>354078</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>341343</t>
+          <t>341679</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>358844</t>
+          <t>359458</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>690083</t>
+          <t>691685</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>710312</t>
+          <t>711276</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,54%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7045</t>
+          <t>7142</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20734</t>
+          <t>20598</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11744</t>
+          <t>11253</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29937</t>
+          <t>28771</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22884</t>
+          <t>22992</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44645</t>
+          <t>44680</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>182574</t>
+          <t>182710</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>196263</t>
+          <t>196166</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>177731</t>
+          <t>178897</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>195924</t>
+          <t>196415</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>366331</t>
+          <t>366296</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>388092</t>
+          <t>387984</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,41%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5623</t>
+          <t>5608</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18299</t>
+          <t>17664</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21270</t>
+          <t>20812</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>42114</t>
+          <t>41407</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>30059</t>
+          <t>29999</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>54609</t>
+          <t>54059</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,85%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>252512</t>
+          <t>253147</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265188</t>
+          <t>265203</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>236030</t>
+          <t>236737</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>256874</t>
+          <t>257332</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>494346</t>
+          <t>494896</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>518896</t>
+          <t>518956</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,54%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25298</t>
+          <t>24981</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49482</t>
+          <t>49589</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>41433</t>
+          <t>40702</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>68901</t>
+          <t>68452</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>71539</t>
+          <t>71182</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>106428</t>
+          <t>108854</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>565545</t>
+          <t>565438</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>589729</t>
+          <t>590046</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>569318</t>
+          <t>569767</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>596786</t>
+          <t>597517</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1146818</t>
+          <t>1144392</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1181707</t>
+          <t>1182064</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,32%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17195</t>
+          <t>17018</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>36794</t>
+          <t>37066</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>36801</t>
+          <t>35982</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>65431</t>
+          <t>64259</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>60554</t>
+          <t>59551</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>93643</t>
+          <t>94137</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>707001</t>
+          <t>706729</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>726600</t>
+          <t>726777</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>718080</t>
+          <t>719252</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>746710</t>
+          <t>747529</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1433663</t>
+          <t>1433169</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1466752</t>
+          <t>1467755</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,1%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>114463</t>
+          <t>114249</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>161027</t>
+          <t>160390</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>221883</t>
+          <t>221283</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>285315</t>
+          <t>281499</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>350217</t>
+          <t>347926</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>422044</t>
+          <t>424115</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3114572</t>
+          <t>3115209</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3161136</t>
+          <t>3161350</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3093882</t>
+          <t>3097698</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3157314</t>
+          <t>3157914</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6232752</t>
+          <t>6230681</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6304579</t>
+          <t>6306870</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,77%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses en 2012</t>
+          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses en 2012 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16141</t>
+          <t>16151</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35959</t>
+          <t>37204</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26264</t>
+          <t>26422</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50079</t>
+          <t>50291</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47668</t>
+          <t>48222</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79499</t>
+          <t>81116</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>257534</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>278597</t>
+          <t>278587</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>237166</t>
+          <t>236954</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>260981</t>
+          <t>260823</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>502484</t>
+          <t>500867</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>534315</t>
+          <t>533761</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,71%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30917</t>
+          <t>30220</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58779</t>
+          <t>55973</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45621</t>
+          <t>44327</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75321</t>
+          <t>75542</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>82554</t>
+          <t>84342</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>123641</t>
+          <t>125147</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>444701</t>
+          <t>447507</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>472563</t>
+          <t>473260</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>448444</t>
+          <t>448223</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>478144</t>
+          <t>479438</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>903604</t>
+          <t>902098</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>944691</t>
+          <t>942903</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,79%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16435</t>
+          <t>15053</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35948</t>
+          <t>35384</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24725</t>
+          <t>25509</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48306</t>
+          <t>49400</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47176</t>
+          <t>47232</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>76997</t>
+          <t>78392</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,79%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>288098</t>
+          <t>288662</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>307611</t>
+          <t>308993</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>292714</t>
+          <t>291620</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>316295</t>
+          <t>315511</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>588069</t>
+          <t>586674</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>617890</t>
+          <t>617834</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,9%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12448</t>
+          <t>12076</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29258</t>
+          <t>30552</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26980</t>
+          <t>28085</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51709</t>
+          <t>51973</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44302</t>
+          <t>44174</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74754</t>
+          <t>74779</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>344724</t>
+          <t>343430</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>361534</t>
+          <t>361906</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>337242</t>
+          <t>336978</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>361971</t>
+          <t>360866</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>688179</t>
+          <t>688154</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>718631</t>
+          <t>718759</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,21%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7850</t>
+          <t>7326</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22541</t>
+          <t>22315</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13584</t>
+          <t>13545</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31553</t>
+          <t>31253</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24621</t>
+          <t>25056</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46965</t>
+          <t>48565</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>190077</t>
+          <t>190303</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>204768</t>
+          <t>205292</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>188038</t>
+          <t>188338</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>206007</t>
+          <t>206046</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>385244</t>
+          <t>383644</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>407588</t>
+          <t>407153</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,2%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8273</t>
+          <t>8394</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24526</t>
+          <t>27264</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18638</t>
+          <t>16679</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>38327</t>
+          <t>37151</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>30253</t>
+          <t>30725</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>55845</t>
+          <t>55110</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,95%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>249455</t>
+          <t>246717</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265708</t>
+          <t>265587</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>241704</t>
+          <t>242880</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>261393</t>
+          <t>263352</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>498167</t>
+          <t>498902</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>523759</t>
+          <t>523287</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,45%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20788</t>
+          <t>21444</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>43520</t>
+          <t>45858</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44247</t>
+          <t>44985</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>76653</t>
+          <t>74690</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>69801</t>
+          <t>71080</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>109045</t>
+          <t>109840</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>619268</t>
+          <t>616930</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>642000</t>
+          <t>641344</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>617200</t>
+          <t>619163</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>649606</t>
+          <t>648868</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1247596</t>
+          <t>1246801</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1286840</t>
+          <t>1285561</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,76%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>26620</t>
+          <t>25922</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>50723</t>
+          <t>50633</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>47155</t>
+          <t>46737</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>77511</t>
+          <t>78440</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>79903</t>
+          <t>78746</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>119808</t>
+          <t>117635</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>728375</t>
+          <t>728465</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>752478</t>
+          <t>753176</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>746342</t>
+          <t>745413</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>776698</t>
+          <t>777116</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1483143</t>
+          <t>1485316</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1523048</t>
+          <t>1524205</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>181142</t>
+          <t>179576</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>240563</t>
+          <t>238955</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>304031</t>
+          <t>305250</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>374818</t>
+          <t>377915</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>501689</t>
+          <t>498597</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>591963</t>
+          <t>594004</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3184168</t>
+          <t>3185776</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3243589</t>
+          <t>3245155</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3183491</t>
+          <t>3180394</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3254278</t>
+          <t>3253059</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6391077</t>
+          <t>6389036</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6481351</t>
+          <t>6484443</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,86%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses en 2016</t>
+          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8921</t>
+          <t>9275</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25432</t>
+          <t>24593</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23724</t>
+          <t>24106</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46294</t>
+          <t>45951</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37690</t>
+          <t>37498</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65070</t>
+          <t>63841</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,96%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>268329</t>
+          <t>269168</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>284840</t>
+          <t>284486</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>242409</t>
+          <t>242752</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>264979</t>
+          <t>264597</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>517394</t>
+          <t>518623</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>544774</t>
+          <t>544966</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,56%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13807</t>
+          <t>13360</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31583</t>
+          <t>31514</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25012</t>
+          <t>25758</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50136</t>
+          <t>50201</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40917</t>
+          <t>42505</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71785</t>
+          <t>73082</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>470992</t>
+          <t>471061</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>488768</t>
+          <t>489215</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>472948</t>
+          <t>472883</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>498072</t>
+          <t>497326</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>953874</t>
+          <t>952577</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>984742</t>
+          <t>983154</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,86%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4572</t>
+          <t>4666</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16027</t>
+          <t>16553</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23471</t>
+          <t>23529</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46610</t>
+          <t>45695</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32139</t>
+          <t>30856</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57495</t>
+          <t>55847</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>302538</t>
+          <t>302012</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>313993</t>
+          <t>313899</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>289699</t>
+          <t>290614</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>312838</t>
+          <t>312780</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>597379</t>
+          <t>599027</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>622735</t>
+          <t>624018</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,29%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18127</t>
+          <t>18873</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39228</t>
+          <t>40134</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20938</t>
+          <t>21549</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44310</t>
+          <t>44446</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45817</t>
+          <t>45130</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>77686</t>
+          <t>77762</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>330736</t>
+          <t>329830</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>351837</t>
+          <t>351091</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>342973</t>
+          <t>342837</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>366345</t>
+          <t>365734</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>679561</t>
+          <t>679485</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>711430</t>
+          <t>712117</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,04%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>3864</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16320</t>
+          <t>15110</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5467</t>
+          <t>5919</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19781</t>
+          <t>19725</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12978</t>
+          <t>12482</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31597</t>
+          <t>32113</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>194901</t>
+          <t>196111</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>206750</t>
+          <t>207357</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>198806</t>
+          <t>198862</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>213120</t>
+          <t>212668</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>398211</t>
+          <t>397695</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>416830</t>
+          <t>417326</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,1%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12072</t>
+          <t>11792</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29603</t>
+          <t>28900</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18915</t>
+          <t>18485</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41687</t>
+          <t>40195</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>34374</t>
+          <t>34427</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>61052</t>
+          <t>63174</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,78%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>233520</t>
+          <t>234223</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>251051</t>
+          <t>251331</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>231428</t>
+          <t>232920</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>254200</t>
+          <t>254630</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>475186</t>
+          <t>473064</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>501864</t>
+          <t>501811</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,58%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16100</t>
+          <t>17402</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38897</t>
+          <t>39699</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>36585</t>
+          <t>35242</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>66330</t>
+          <t>65287</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>58833</t>
+          <t>58346</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>93931</t>
+          <t>95353</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>617661</t>
+          <t>616859</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>640458</t>
+          <t>639156</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>624964</t>
+          <t>626007</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>654709</t>
+          <t>656052</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1253921</t>
+          <t>1252499</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1289019</t>
+          <t>1289506</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,67%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25353</t>
+          <t>25453</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>49509</t>
+          <t>49533</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>36857</t>
+          <t>36083</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>64692</t>
+          <t>65338</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>66656</t>
+          <t>68657</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>103906</t>
+          <t>105726</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>729074</t>
+          <t>729050</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>753230</t>
+          <t>753130</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9913,7 +9913,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>761475</t>
+          <t>760829</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>789310</t>
+          <t>790084</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1500844</t>
+          <t>1499024</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1538094</t>
+          <t>1536093</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,72%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>138465</t>
+          <t>138742</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>190218</t>
+          <t>189650</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>241903</t>
+          <t>242355</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>306475</t>
+          <t>309016</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>396890</t>
+          <t>396945</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>477952</t>
+          <t>480834</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3204132</t>
+          <t>3204700</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3255885</t>
+          <t>3255608</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3238067</t>
+          <t>3235526</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3302639</t>
+          <t>3302187</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6460940</t>
+          <t>6458058</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6542002</t>
+          <t>6541947</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses en 2023</t>
+          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses en 2023 (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6499</t>
+          <t>7134</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19841</t>
+          <t>20808</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13045</t>
+          <t>13449</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25851</t>
+          <t>25764</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22687</t>
+          <t>23018</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42193</t>
+          <t>40852</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>291602</t>
+          <t>290635</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>304944</t>
+          <t>304309</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>263784</t>
+          <t>263871</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>276590</t>
+          <t>276186</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>558884</t>
+          <t>560225</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>578390</t>
+          <t>578059</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,17%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28080</t>
+          <t>25820</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53352</t>
+          <t>52692</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14567</t>
+          <t>14957</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31953</t>
+          <t>33271</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46925</t>
+          <t>47293</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>76807</t>
+          <t>79249</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>465038</t>
+          <t>465698</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>490310</t>
+          <t>492570</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>483016</t>
+          <t>481698</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>500402</t>
+          <t>500012</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>956552</t>
+          <t>954110</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>986434</t>
+          <t>986066</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,42%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19122</t>
+          <t>18781</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37797</t>
+          <t>37206</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24775</t>
+          <t>23811</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43653</t>
+          <t>43266</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48158</t>
+          <t>47699</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>75651</t>
+          <t>73700</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,08%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>278253</t>
+          <t>278844</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>296928</t>
+          <t>297269</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>305475</t>
+          <t>305862</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>324353</t>
+          <t>325317</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>589527</t>
+          <t>591478</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>617020</t>
+          <t>617479</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,83%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14474</t>
+          <t>14266</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38358</t>
+          <t>36127</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18844</t>
+          <t>18332</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52517</t>
+          <t>50870</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38791</t>
+          <t>37512</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>79490</t>
+          <t>77599</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>274199</t>
+          <t>276430</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>298083</t>
+          <t>298291</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>423201</t>
+          <t>424848</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>456874</t>
+          <t>457386</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>708784</t>
+          <t>710675</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>749483</t>
+          <t>750762</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,24%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7893</t>
+          <t>8083</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5255</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12609</t>
+          <t>12454</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8683</t>
+          <t>8529</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17886</t>
+          <t>18296</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>170849</t>
+          <t>170659</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>176826</t>
+          <t>176835</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>196047</t>
+          <t>196202</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>203401</t>
+          <t>203471</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>369512</t>
+          <t>369102</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>378715</t>
+          <t>378869</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17816</t>
+          <t>17438</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33389</t>
+          <t>33372</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,7 +12432,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15841</t>
+          <t>15196</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29789</t>
+          <t>29704</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35719</t>
+          <t>35820</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>57539</t>
+          <t>57484</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,91%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>236247</t>
+          <t>236264</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>251820</t>
+          <t>252198</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12550,7 +12550,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>227267</t>
+          <t>227352</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>241215</t>
+          <t>241860</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>469153</t>
+          <t>469208</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>490973</t>
+          <t>490872</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,2%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25427</t>
+          <t>25296</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47037</t>
+          <t>47363</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23469</t>
+          <t>23121</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>71728</t>
+          <t>72584</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>53088</t>
+          <t>54117</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>108383</t>
+          <t>107958</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>577242</t>
+          <t>576916</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>598852</t>
+          <t>598983</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>777537</t>
+          <t>776681</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>825796</t>
+          <t>826144</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1365161</t>
+          <t>1365586</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1420456</t>
+          <t>1419427</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,33%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9137</t>
+          <t>10070</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>35857</t>
+          <t>36740</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20811</t>
+          <t>19854</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>39772</t>
+          <t>38869</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>29810</t>
+          <t>31605</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>67320</t>
+          <t>69659</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>892863</t>
+          <t>891980</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>919583</t>
+          <t>918650</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>675620</t>
+          <t>676523</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>694581</t>
+          <t>695538</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1576792</t>
+          <t>1574453</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1614302</t>
+          <t>1612507</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,08%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>148604</t>
+          <t>147065</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>219461</t>
+          <t>219115</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>177874</t>
+          <t>175872</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>249496</t>
+          <t>249986</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,47 +13496,47 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
+          <t>4,81%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>6,83%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>404902</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>346082</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>448675</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>5,69%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
           <t>4,86%</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>6,82%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>572</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>404902</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>348675</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>450091</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>5,69%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3240356</t>
+          <t>3240702</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3311213</t>
+          <t>3312752</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3410321</t>
+          <t>3409831</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3481943</t>
+          <t>3483945</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,47 +13609,47 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
+          <t>95,19%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>8167</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>6714732</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>6670959</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>6773552</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>94,31%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>93,7%</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
           <t>95,14%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>8167</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>6714732</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>6669543</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>6770959</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>94,31%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>93,68%</t>
-        </is>
-      </c>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t>95,1%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P20-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P20-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5505</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17637</t>
+          <t>17838</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6875</t>
+          <t>6009</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21672</t>
+          <t>21637</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14306</t>
+          <t>15214</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34068</t>
+          <t>34770</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>255373</t>
+          <t>255172</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>267608</t>
+          <t>267505</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>239166</t>
+          <t>239201</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>253963</t>
+          <t>254829</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>499780</t>
+          <t>499078</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>519542</t>
+          <t>518634</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,15%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17659</t>
+          <t>16599</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38106</t>
+          <t>38134</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34725</t>
+          <t>35539</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60453</t>
+          <t>61405</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58154</t>
+          <t>57571</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>90188</t>
+          <t>91396</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>454969</t>
+          <t>454941</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>475416</t>
+          <t>476476</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>443496</t>
+          <t>442544</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>469224</t>
+          <t>468410</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>906836</t>
+          <t>905628</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>938870</t>
+          <t>939453</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,23%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16774</t>
+          <t>15058</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9362</t>
+          <t>9806</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24675</t>
+          <t>25321</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15851</t>
+          <t>15279</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36714</t>
+          <t>35790</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>302072</t>
+          <t>303788</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>315302</t>
+          <t>315955</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>310737</t>
+          <t>310091</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>326050</t>
+          <t>325606</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>617544</t>
+          <t>618468</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>638407</t>
+          <t>638979</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,66%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>3447</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14584</t>
+          <t>13894</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11998</t>
+          <t>12290</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29777</t>
+          <t>29390</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17907</t>
+          <t>17089</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37498</t>
+          <t>37503</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>343143</t>
+          <t>343833</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>354078</t>
+          <t>354280</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>341679</t>
+          <t>342066</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>359458</t>
+          <t>359166</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>691685</t>
+          <t>691680</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>711276</t>
+          <t>712094</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,66%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7142</t>
+          <t>7752</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20598</t>
+          <t>21780</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11253</t>
+          <t>11150</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28771</t>
+          <t>28515</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22992</t>
+          <t>21784</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44680</t>
+          <t>42929</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,45%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>182710</t>
+          <t>181528</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>196166</t>
+          <t>195556</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>178897</t>
+          <t>179153</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>196415</t>
+          <t>196518</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>366296</t>
+          <t>368047</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>387984</t>
+          <t>389192</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,7%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5608</t>
+          <t>5686</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17664</t>
+          <t>17925</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20812</t>
+          <t>21288</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41407</t>
+          <t>42320</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,47 +2498,47 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
+          <t>7,65%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>15,22%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>41038</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>30920</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>54276</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
           <t>7,48%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>14,89%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>41038</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>29999</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>54059</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>7,48%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253147</t>
+          <t>252886</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265203</t>
+          <t>265125</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>236737</t>
+          <t>235824</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>257332</t>
+          <t>256856</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,47 +2611,47 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
+          <t>92,35%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>496</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>507917</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>494679</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>518035</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
           <t>92,52%</t>
         </is>
       </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>496</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>507917</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>494896</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>518956</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>92,52%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,37%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24981</t>
+          <t>25963</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49589</t>
+          <t>48451</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40702</t>
+          <t>41133</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>68452</t>
+          <t>68911</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>71182</t>
+          <t>72120</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>108854</t>
+          <t>108763</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,68%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>565438</t>
+          <t>566576</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>590046</t>
+          <t>589064</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>569767</t>
+          <t>569308</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>597517</t>
+          <t>597086</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1144392</t>
+          <t>1144483</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1182064</t>
+          <t>1181126</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,25%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17018</t>
+          <t>17803</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37066</t>
+          <t>37486</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>35982</t>
+          <t>37952</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>64259</t>
+          <t>66380</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>59551</t>
+          <t>59726</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>94137</t>
+          <t>94225</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>706729</t>
+          <t>706309</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>726777</t>
+          <t>725992</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>719252</t>
+          <t>717131</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>747529</t>
+          <t>745559</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1433169</t>
+          <t>1433081</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1467755</t>
+          <t>1467580</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,09%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>114249</t>
+          <t>113852</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>160390</t>
+          <t>161439</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>221283</t>
+          <t>217521</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>281499</t>
+          <t>281291</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>347926</t>
+          <t>345434</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>424115</t>
+          <t>423699</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3115209</t>
+          <t>3114160</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3161350</t>
+          <t>3161747</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3097698</t>
+          <t>3097906</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3157914</t>
+          <t>3161676</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6230681</t>
+          <t>6231097</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6306870</t>
+          <t>6309362</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,81%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16151</t>
+          <t>16941</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37204</t>
+          <t>37212</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26422</t>
+          <t>26772</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50291</t>
+          <t>50689</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48222</t>
+          <t>49748</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81116</t>
+          <t>80256</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,79%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>257534</t>
+          <t>257526</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>278587</t>
+          <t>277797</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>236954</t>
+          <t>236556</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>260823</t>
+          <t>260473</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>500867</t>
+          <t>501727</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>533761</t>
+          <t>532235</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,45%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30220</t>
+          <t>29836</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55973</t>
+          <t>57602</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44327</t>
+          <t>45690</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75542</t>
+          <t>74151</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>84342</t>
+          <t>83970</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>125147</t>
+          <t>124612</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,13%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>447507</t>
+          <t>445878</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>473260</t>
+          <t>473644</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>448223</t>
+          <t>449614</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>479438</t>
+          <t>478075</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>902098</t>
+          <t>902633</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>942903</t>
+          <t>943275</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,83%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15053</t>
+          <t>15884</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35384</t>
+          <t>35185</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25509</t>
+          <t>25893</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49400</t>
+          <t>48501</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47232</t>
+          <t>47642</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78392</t>
+          <t>77943</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,72%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>288662</t>
+          <t>288861</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>308993</t>
+          <t>308162</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>291620</t>
+          <t>292519</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>315511</t>
+          <t>315127</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>586674</t>
+          <t>587123</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>617834</t>
+          <t>617424</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,84%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12076</t>
+          <t>12616</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30552</t>
+          <t>29661</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28085</t>
+          <t>27911</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51973</t>
+          <t>51778</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44174</t>
+          <t>45639</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74779</t>
+          <t>75169</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,85%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>343430</t>
+          <t>344321</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>361906</t>
+          <t>361366</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>336978</t>
+          <t>337173</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>360866</t>
+          <t>361040</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>688154</t>
+          <t>687764</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>718759</t>
+          <t>717294</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,02%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7326</t>
+          <t>7895</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22315</t>
+          <t>21874</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13545</t>
+          <t>13343</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31253</t>
+          <t>31688</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25056</t>
+          <t>25228</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48565</t>
+          <t>49319</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>190303</t>
+          <t>190744</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>205292</t>
+          <t>204723</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>188338</t>
+          <t>187903</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>206046</t>
+          <t>206248</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>383644</t>
+          <t>382890</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>407153</t>
+          <t>406981</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,16%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8394</t>
+          <t>8455</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27264</t>
+          <t>25521</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16679</t>
+          <t>18037</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37151</t>
+          <t>38572</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>30725</t>
+          <t>30937</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>55110</t>
+          <t>56301</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,16%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>246717</t>
+          <t>248460</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265587</t>
+          <t>265526</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>242880</t>
+          <t>241459</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>263352</t>
+          <t>261994</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>498902</t>
+          <t>497711</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>523287</t>
+          <t>523075</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,42%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21444</t>
+          <t>20357</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45858</t>
+          <t>44106</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44985</t>
+          <t>45596</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>74690</t>
+          <t>75307</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>71080</t>
+          <t>70484</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>109840</t>
+          <t>112850</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>616930</t>
+          <t>618682</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>641344</t>
+          <t>642431</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>619163</t>
+          <t>618546</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>648868</t>
+          <t>648257</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1246801</t>
+          <t>1243791</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1285561</t>
+          <t>1286157</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,8%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25922</t>
+          <t>26515</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>50633</t>
+          <t>50732</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>46737</t>
+          <t>46566</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>78440</t>
+          <t>77416</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>78746</t>
+          <t>79743</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>117635</t>
+          <t>120072</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>728465</t>
+          <t>728366</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>753176</t>
+          <t>752583</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>745413</t>
+          <t>746437</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>777116</t>
+          <t>777287</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1485316</t>
+          <t>1482879</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1524205</t>
+          <t>1523208</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,03%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>179576</t>
+          <t>182917</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>238955</t>
+          <t>241405</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>305250</t>
+          <t>304653</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>377915</t>
+          <t>372775</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>498597</t>
+          <t>501056</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>594004</t>
+          <t>597539</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3185776</t>
+          <t>3183326</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3245155</t>
+          <t>3241814</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3180394</t>
+          <t>3185534</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3253059</t>
+          <t>3253656</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6389036</t>
+          <t>6385501</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6484443</t>
+          <t>6481984</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,82%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9275</t>
+          <t>8883</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24593</t>
+          <t>23612</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24106</t>
+          <t>23418</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45951</t>
+          <t>45349</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37498</t>
+          <t>36684</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63841</t>
+          <t>64662</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>269168</t>
+          <t>270149</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>284486</t>
+          <t>284878</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>242752</t>
+          <t>243354</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>264597</t>
+          <t>265285</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>518623</t>
+          <t>517802</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>544966</t>
+          <t>545780</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,7%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13360</t>
+          <t>13319</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31514</t>
+          <t>32165</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25758</t>
+          <t>25010</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50201</t>
+          <t>47910</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42505</t>
+          <t>42494</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73082</t>
+          <t>72878</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>471061</t>
+          <t>470410</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>489215</t>
+          <t>489256</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>472883</t>
+          <t>475174</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>497326</t>
+          <t>498074</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>952577</t>
+          <t>952781</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>983154</t>
+          <t>983165</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4666</t>
+          <t>4594</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16553</t>
+          <t>16641</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23529</t>
+          <t>23377</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45695</t>
+          <t>44706</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30856</t>
+          <t>31376</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55847</t>
+          <t>56275</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>302012</t>
+          <t>301924</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>313899</t>
+          <t>313971</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>290614</t>
+          <t>291603</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>312780</t>
+          <t>312932</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>599027</t>
+          <t>598599</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>624018</t>
+          <t>623498</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,21%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18873</t>
+          <t>19423</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40134</t>
+          <t>39747</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21549</t>
+          <t>22096</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44446</t>
+          <t>44648</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45130</t>
+          <t>44709</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>77762</t>
+          <t>77265</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,2%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>329830</t>
+          <t>330217</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>351091</t>
+          <t>350541</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>342837</t>
+          <t>342635</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>365734</t>
+          <t>365187</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>679485</t>
+          <t>679982</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>712117</t>
+          <t>712538</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,1%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3864</t>
+          <t>4675</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15110</t>
+          <t>15041</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5919</t>
+          <t>5465</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19725</t>
+          <t>20327</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12482</t>
+          <t>12384</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32113</t>
+          <t>29895</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>196111</t>
+          <t>196180</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>207357</t>
+          <t>206546</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>198862</t>
+          <t>198260</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>212668</t>
+          <t>213122</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>397695</t>
+          <t>399913</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>417326</t>
+          <t>417424</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11792</t>
+          <t>12018</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28900</t>
+          <t>29223</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18485</t>
+          <t>19247</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40195</t>
+          <t>40518</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>34427</t>
+          <t>36599</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>63174</t>
+          <t>61742</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,51%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>234223</t>
+          <t>233900</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>251331</t>
+          <t>251105</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>232920</t>
+          <t>232597</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>254630</t>
+          <t>253868</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>473064</t>
+          <t>474496</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>501811</t>
+          <t>499639</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,17%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17402</t>
+          <t>16955</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39699</t>
+          <t>38936</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35242</t>
+          <t>35836</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>65287</t>
+          <t>65700</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>58346</t>
+          <t>59138</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>95353</t>
+          <t>95139</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>616859</t>
+          <t>617622</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>639156</t>
+          <t>639603</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>626007</t>
+          <t>625594</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>656052</t>
+          <t>655458</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1252499</t>
+          <t>1252713</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1289506</t>
+          <t>1288714</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,61%</t>
         </is>
       </c>
     </row>
@@ -9780,47 +9780,47 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25453</t>
+          <t>25062</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
+          <t>49545</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>4,59%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>3,22%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>6,36%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
           <t>49533</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>4,59%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>3,27%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>6,36%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>49533</t>
-        </is>
-      </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>36083</t>
+          <t>36261</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>65338</t>
+          <t>64275</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>68657</t>
+          <t>67899</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>105726</t>
+          <t>105249</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>729050</t>
+          <t>729038</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>753130</t>
+          <t>753521</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9913,7 +9913,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>760829</t>
+          <t>761892</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>790084</t>
+          <t>789906</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1499024</t>
+          <t>1499501</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1536093</t>
+          <t>1536851</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,77%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>138742</t>
+          <t>140882</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>189650</t>
+          <t>189532</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>242355</t>
+          <t>243318</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>309016</t>
+          <t>308758</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>396945</t>
+          <t>395829</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>480834</t>
+          <t>484261</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3204700</t>
+          <t>3204818</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3255608</t>
+          <t>3253468</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3235526</t>
+          <t>3235784</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3302187</t>
+          <t>3301224</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6458058</t>
+          <t>6454631</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6541947</t>
+          <t>6543063</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,3%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>12044</t>
+          <t>11673</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7134</t>
+          <t>6394</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20808</t>
+          <t>19267</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>18894</t>
+          <t>22209</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13449</t>
+          <t>16086</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25764</t>
+          <t>30616</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>30938</t>
+          <t>33882</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23018</t>
+          <t>25876</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40852</t>
+          <t>45025</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>299399</t>
+          <t>307172</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>290635</t>
+          <t>299578</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>304309</t>
+          <t>312451</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>270741</t>
+          <t>293852</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>263871</t>
+          <t>285445</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>276186</t>
+          <t>299975</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>570139</t>
+          <t>601024</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>560225</t>
+          <t>589881</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>578059</t>
+          <t>609030</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>95,92%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>38744</t>
+          <t>40940</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25820</t>
+          <t>28770</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52692</t>
+          <t>56863</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22411</t>
+          <t>24396</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14957</t>
+          <t>16359</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33271</t>
+          <t>35004</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>61155</t>
+          <t>65335</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47293</t>
+          <t>50023</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>79249</t>
+          <t>83107</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>479646</t>
+          <t>489707</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>465698</t>
+          <t>473784</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>492570</t>
+          <t>501877</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>492558</t>
+          <t>522098</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>481698</t>
+          <t>511490</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>500012</t>
+          <t>530135</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>972204</t>
+          <t>1011806</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>954110</t>
+          <t>994034</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>986066</t>
+          <t>1027118</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,36%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>27141</t>
+          <t>26594</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18781</t>
+          <t>19195</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37206</t>
+          <t>38386</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>32844</t>
+          <t>33263</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23811</t>
+          <t>23705</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43266</t>
+          <t>43599</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>59985</t>
+          <t>59857</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47699</t>
+          <t>47983</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73700</t>
+          <t>74263</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,04%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>288909</t>
+          <t>289399</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>278844</t>
+          <t>277607</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>297269</t>
+          <t>296798</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>316284</t>
+          <t>323118</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>305862</t>
+          <t>312782</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>325317</t>
+          <t>332676</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>605193</t>
+          <t>612518</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>591478</t>
+          <t>598112</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>617479</t>
+          <t>624392</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,86%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>23237</t>
+          <t>27654</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14266</t>
+          <t>18463</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36127</t>
+          <t>45676</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>33638</t>
+          <t>38211</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18332</t>
+          <t>26644</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50870</t>
+          <t>57004</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>56875</t>
+          <t>65865</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37512</t>
+          <t>48915</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>77599</t>
+          <t>90493</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>11,38%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>289320</t>
+          <t>345491</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>276430</t>
+          <t>327469</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>298291</t>
+          <t>354682</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>442080</t>
+          <t>383750</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>424848</t>
+          <t>364957</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>457386</t>
+          <t>395317</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>731399</t>
+          <t>729242</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>710675</t>
+          <t>704614</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>750762</t>
+          <t>746192</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>93,85%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4308</t>
+          <t>4533</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>2154</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8083</t>
+          <t>8668</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8257</t>
+          <t>8980</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>5726</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12454</t>
+          <t>13270</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>12565</t>
+          <t>13513</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8529</t>
+          <t>9110</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18296</t>
+          <t>19371</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>174434</t>
+          <t>201132</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>170659</t>
+          <t>196997</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>176835</t>
+          <t>203511</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>200399</t>
+          <t>218235</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>196202</t>
+          <t>213945</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>203471</t>
+          <t>221489</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>374833</t>
+          <t>419366</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>369102</t>
+          <t>413508</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>378869</t>
+          <t>423769</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>24252</t>
+          <t>24261</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17438</t>
+          <t>17920</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33372</t>
+          <t>32736</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>21577</t>
+          <t>22302</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15196</t>
+          <t>15917</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29704</t>
+          <t>29684</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>45830</t>
+          <t>46563</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35820</t>
+          <t>35761</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>57484</t>
+          <t>57777</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>245384</t>
+          <t>246446</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>236264</t>
+          <t>237971</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>252198</t>
+          <t>252787</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>235479</t>
+          <t>241448</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>227352</t>
+          <t>234066</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>241860</t>
+          <t>247833</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>480862</t>
+          <t>487894</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>469208</t>
+          <t>476680</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>490872</t>
+          <t>498696</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,31%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>35242</t>
+          <t>43422</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25296</t>
+          <t>30726</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47363</t>
+          <t>56984</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>50835</t>
+          <t>63813</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23121</t>
+          <t>49638</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>72584</t>
+          <t>77503</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>86077</t>
+          <t>107235</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>54117</t>
+          <t>90130</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>107958</t>
+          <t>128326</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>589037</t>
+          <t>676265</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>576916</t>
+          <t>662703</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>598983</t>
+          <t>688961</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>798430</t>
+          <t>708244</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>776681</t>
+          <t>694554</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>826144</t>
+          <t>722419</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1387467</t>
+          <t>1384509</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1365586</t>
+          <t>1363418</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1419427</t>
+          <t>1401614</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>93,96%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>23090</t>
+          <t>26101</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>17852</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>36740</t>
+          <t>37842</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>28387</t>
+          <t>32294</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19854</t>
+          <t>22802</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>38869</t>
+          <t>44335</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>51477</t>
+          <t>58395</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>31605</t>
+          <t>44596</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>69659</t>
+          <t>73680</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>905630</t>
+          <t>771971</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>891980</t>
+          <t>760230</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>918650</t>
+          <t>780220</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>687005</t>
+          <t>798315</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>676523</t>
+          <t>786274</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>695538</t>
+          <t>807807</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1592635</t>
+          <t>1570286</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1574453</t>
+          <t>1555001</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1612507</t>
+          <t>1584085</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>188058</t>
+          <t>205178</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>147065</t>
+          <t>179132</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>219115</t>
+          <t>233033</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>216843</t>
+          <t>245467</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>175872</t>
+          <t>218887</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>249986</t>
+          <t>275599</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>404902</t>
+          <t>450645</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>346082</t>
+          <t>411442</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>448675</t>
+          <t>487883</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3271759</t>
+          <t>3327584</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3240702</t>
+          <t>3299729</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3312752</t>
+          <t>3353630</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3442974</t>
+          <t>3489062</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3409831</t>
+          <t>3458930</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3483945</t>
+          <t>3515642</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6714732</t>
+          <t>6816646</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6670959</t>
+          <t>6779408</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6773552</t>
+          <t>6855849</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>94,34%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3659817</t>
+          <t>3734529</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3659817</t>
+          <t>3734529</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3659817</t>
+          <t>3734529</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7119634</t>
+          <t>7267291</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7119634</t>
+          <t>7267291</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7119634</t>
+          <t>7267291</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
